--- a/docs/literature_db/PFAS_rice_parameter_database.xlsx
+++ b/docs/literature_db/PFAS_rice_parameter_database.xlsx
@@ -1293,7 +1293,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>flooded paddy; Andosol (volcanic ash, high OC); field</t>
+          <t>paddy field at harvest; SOC 0.73-2.66% (mean 1.19%, SI Table S2) - NOT Andosol (that was Yamazaki); field</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -2373,6 +2373,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -2574,7 +2575,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>low; ~0.1-0.25 typical (genotype-dependent)</t>
+          <t>Nada 2018 gives 0.18-0.80 on a FRESH-weight basis (wire-mesh field beds, not flooded paddy; 3 cultivars) - it does NOT support "0.1-0.25 typical". Flooded-paddy DRY-weight anchor: Kim 2001 FACE (Akitakomachi) 0.12-0.14 at PI, 0.026-0.033 at maturity (15-20 cm soil blocks -&gt; a floor)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -2604,7 +2605,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>Roots are a SMALL fraction of biomass -&gt; M_root small vs shoot. Increases under drought; here paddy is flooded (low R/S).</t>
+          <t>Read at source (sampling-protocol audit, docs/sampling_protocols_audit_KR.md). Roots are a SMALL fraction of biomass -&gt; M_root small vs shoot; increases under drought/low N. Paddy DW values: docs/literature_db/raw_si/rice_organ_biomass_literature.csv.</t>
         </is>
       </c>
     </row>
@@ -2937,6 +2938,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
@@ -3146,6 +3148,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
@@ -5032,6 +5035,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -5716,6 +5720,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
@@ -5995,6 +6000,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
@@ -6205,6 +6211,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -7003,6 +7010,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
@@ -7327,6 +7335,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
@@ -7510,6 +7519,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -8137,6 +8147,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
@@ -8386,6 +8397,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
